--- a/diseases/d203/2010-2014.xlsx
+++ b/diseases/d203/2010-2014.xlsx
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25042,7 +25042,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33272,7 +33272,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34626,7 +34626,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -35028,7 +35028,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35578,7 +35578,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36382,7 +36382,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37334,7 +37334,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38942,7 +38942,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40698,7 +40698,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41650,7 +41650,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -42052,7 +42052,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42454,7 +42454,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42856,7 +42856,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46918,7 +46918,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47320,7 +47320,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47722,7 +47722,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48124,7 +48124,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48526,7 +48526,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49076,7 +49076,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49880,7 +49880,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50832,7 +50832,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51234,7 +51234,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52038,7 +52038,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53392,7 +53392,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53794,7 +53794,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54196,7 +54196,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54746,7 +54746,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55148,7 +55148,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55550,7 +55550,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55952,7 +55952,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d203/2010-2014.xlsx
+++ b/diseases/d203/2010-2014.xlsx
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23688,7 +23688,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24640,7 +24640,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25042,7 +25042,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25846,7 +25846,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26396,7 +26396,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27602,7 +27602,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28554,7 +28554,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29358,7 +29358,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30712,7 +30712,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -33272,7 +33272,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -34224,7 +34224,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34626,7 +34626,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -35028,7 +35028,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35578,7 +35578,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36382,7 +36382,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36784,7 +36784,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -37334,7 +37334,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -38138,7 +38138,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38540,7 +38540,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38942,7 +38942,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40698,7 +40698,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41650,7 +41650,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -42052,7 +42052,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42454,7 +42454,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42856,7 +42856,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43808,7 +43808,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45564,7 +45564,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45966,7 +45966,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -46368,7 +46368,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46918,7 +46918,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -47320,7 +47320,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47722,7 +47722,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -48124,7 +48124,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48526,7 +48526,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49076,7 +49076,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49478,7 +49478,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49880,7 +49880,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -50282,7 +50282,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50832,7 +50832,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -51234,7 +51234,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52038,7 +52038,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52588,7 +52588,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52990,7 +52990,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -53392,7 +53392,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53794,7 +53794,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -54196,7 +54196,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54746,7 +54746,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -55148,7 +55148,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55550,7 +55550,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55952,7 +55952,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">

--- a/diseases/d203/2010-2014.xlsx
+++ b/diseases/d203/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3876,9 +3813,6 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4128,7 +4062,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -4278,9 +4212,6 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4530,7 +4461,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -4680,9 +4611,6 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4932,7 +4860,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5079,9 +5007,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5230,9 +5155,6 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5482,7 +5404,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -5632,9 +5554,6 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -5884,7 +5803,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6034,9 +5953,6 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6286,7 +6202,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6436,9 +6352,6 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6688,7 +6601,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -6835,9 +6748,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6986,9 +6896,6 @@
       <c r="P39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -7238,7 +7145,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN40" t="b">
@@ -7388,9 +7295,6 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7640,7 +7544,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -7790,9 +7694,6 @@
       <c r="P43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8042,7 +7943,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -8192,9 +8093,6 @@
       <c r="P45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8444,7 +8342,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -8591,9 +8489,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8742,9 +8637,6 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8994,7 +8886,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9144,9 +9036,6 @@
       <c r="P50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9396,7 +9285,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -9546,9 +9435,6 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9798,7 +9684,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -9948,9 +9834,6 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10200,7 +10083,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10350,9 +10233,6 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10602,7 +10482,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -10749,9 +10629,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -10900,9 +10777,6 @@
       <c r="P59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11152,7 +11026,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -11302,9 +11176,6 @@
       <c r="P61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11554,7 +11425,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -11704,9 +11575,6 @@
       <c r="P63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -11956,7 +11824,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -12106,9 +11974,6 @@
       <c r="P65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12358,7 +12223,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -12505,9 +12370,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12656,9 +12518,6 @@
       <c r="P68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12908,7 +12767,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13058,9 +12917,6 @@
       <c r="P70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13310,7 +13166,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13460,9 +13316,6 @@
       <c r="P72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13712,7 +13565,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -13862,9 +13715,6 @@
       <c r="P74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14114,7 +13964,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14261,9 +14111,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14412,9 +14259,6 @@
       <c r="P77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14664,7 +14508,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14814,9 +14658,6 @@
       <c r="P79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15066,7 +14907,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -15216,9 +15057,6 @@
       <c r="P81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15468,7 +15306,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -15618,9 +15456,6 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15870,7 +15705,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16020,9 +15855,6 @@
       <c r="P85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16272,7 +16104,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -16419,9 +16251,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16570,9 +16399,6 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16822,7 +16648,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16972,9 +16798,6 @@
       <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17224,7 +17047,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -17374,9 +17197,6 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -17626,7 +17446,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -17776,9 +17596,6 @@
       <c r="P94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18028,7 +17845,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -18175,9 +17992,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18326,9 +18140,6 @@
       <c r="P97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18578,7 +18389,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -18728,9 +18539,6 @@
       <c r="P99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18980,7 +18788,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -19130,9 +18938,6 @@
       <c r="P101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -19382,7 +19187,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -19532,9 +19337,6 @@
       <c r="P103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19784,7 +19586,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -19931,9 +19733,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -20082,9 +19881,6 @@
       <c r="P106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20334,7 +20130,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -20484,9 +20280,6 @@
       <c r="P108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20736,7 +20529,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -20886,9 +20679,6 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -21138,7 +20928,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -21288,9 +21078,6 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -21540,7 +21327,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -21690,9 +21477,6 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -21942,7 +21726,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -22089,9 +21873,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -22240,9 +22021,6 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -22492,7 +22270,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -22642,9 +22420,6 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22894,7 +22669,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -23044,9 +22819,6 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -23296,7 +23068,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -23446,9 +23218,6 @@
       <c r="P123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -23698,7 +23467,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -23845,9 +23614,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -23996,9 +23762,6 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -24248,7 +24011,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -24398,9 +24161,6 @@
       <c r="P128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -24650,7 +24410,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -24800,9 +24560,6 @@
       <c r="P130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -25052,7 +24809,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -25202,9 +24959,6 @@
       <c r="P132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -25454,7 +25208,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -25604,9 +25358,6 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -25856,7 +25607,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26003,9 +25754,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -26154,9 +25902,6 @@
       <c r="P137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -26406,7 +26151,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -26556,9 +26301,6 @@
       <c r="P139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26808,7 +26550,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -26958,9 +26700,6 @@
       <c r="P141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -27210,7 +26949,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -27360,9 +27099,6 @@
       <c r="P143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -27612,7 +27348,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -27759,9 +27495,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -27910,9 +27643,6 @@
       <c r="P146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -28162,7 +27892,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -28312,9 +28042,6 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -28564,7 +28291,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -28714,9 +28441,6 @@
       <c r="P150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -28966,7 +28690,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -29116,9 +28840,6 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -29368,7 +29089,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -29515,9 +29236,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -29666,9 +29384,6 @@
       <c r="P155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -29918,7 +29633,7 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN156" t="b">
@@ -30068,9 +29783,6 @@
       <c r="P157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -30320,7 +30032,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -30470,9 +30182,6 @@
       <c r="P159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -30722,7 +30431,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -30872,9 +30581,6 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -31124,7 +30830,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -31274,9 +30980,6 @@
       <c r="P163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -31526,7 +31229,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -31673,9 +31376,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -31824,9 +31524,6 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -32076,7 +31773,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -32226,9 +31923,6 @@
       <c r="P168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -32478,7 +32172,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -32628,9 +32322,6 @@
       <c r="P170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -32880,7 +32571,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -33030,9 +32721,6 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -33282,7 +32970,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -33429,9 +33117,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -33580,9 +33265,6 @@
       <c r="P175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -33832,7 +33514,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -33982,9 +33664,6 @@
       <c r="P177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -34234,7 +33913,7 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN178" t="b">
@@ -34384,9 +34063,6 @@
       <c r="P179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -34636,7 +34312,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -34786,9 +34462,6 @@
       <c r="P181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -35038,7 +34711,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -35185,9 +34858,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -35336,9 +35006,6 @@
       <c r="P184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -35588,7 +35255,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -35738,9 +35405,6 @@
       <c r="P186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -35990,7 +35654,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -36140,9 +35804,6 @@
       <c r="P188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -36392,7 +36053,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -36542,9 +36203,6 @@
       <c r="P190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -36794,7 +36452,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -36941,9 +36599,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -37092,9 +36747,6 @@
       <c r="P193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -37344,7 +36996,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -37494,9 +37146,6 @@
       <c r="P195" t="n">
         <v>0</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
@@ -37746,7 +37395,7 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -37896,9 +37545,6 @@
       <c r="P197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -38148,7 +37794,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -38298,9 +37944,6 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -38550,7 +38193,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -38700,9 +38343,6 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -38952,7 +38592,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -39099,9 +38739,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -39250,9 +38887,6 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -39502,7 +39136,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -39652,9 +39286,6 @@
       <c r="P206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -39904,7 +39535,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -40054,9 +39685,6 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -40306,7 +39934,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -40456,9 +40084,6 @@
       <c r="P210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -40708,7 +40333,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -40855,9 +40480,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -41006,9 +40628,6 @@
       <c r="P213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -41258,7 +40877,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -41408,9 +41027,6 @@
       <c r="P215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -41660,7 +41276,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -41810,9 +41426,6 @@
       <c r="P217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -42062,7 +41675,7 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -42212,9 +41825,6 @@
       <c r="P219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -42464,7 +42074,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -42614,9 +42224,6 @@
       <c r="P221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -42866,7 +42473,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -43013,9 +42620,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -43164,9 +42768,6 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -43416,7 +43017,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -43566,9 +43167,6 @@
       <c r="P226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -43818,7 +43416,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -43968,9 +43566,6 @@
       <c r="P228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -44220,7 +43815,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -44370,9 +43965,6 @@
       <c r="P230" t="n">
         <v>0</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0</v>
       </c>
@@ -44622,7 +44214,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -44769,9 +44361,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -44920,9 +44509,6 @@
       <c r="P233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -45172,7 +44758,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -45322,9 +44908,6 @@
       <c r="P235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -45574,7 +45157,7 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN236" t="b">
@@ -45724,9 +45307,6 @@
       <c r="P237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -45976,7 +45556,7 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN238" t="b">
@@ -46126,9 +45706,6 @@
       <c r="P239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -46378,7 +45955,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -46525,9 +46102,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -46676,9 +46250,6 @@
       <c r="P242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -46928,7 +46499,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -47078,9 +46649,6 @@
       <c r="P244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -47330,7 +46898,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -47480,9 +47048,6 @@
       <c r="P246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -47732,7 +47297,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -47882,9 +47447,6 @@
       <c r="P248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -48134,7 +47696,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -48284,9 +47846,6 @@
       <c r="P250" t="n">
         <v>0</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0</v>
       </c>
@@ -48536,7 +48095,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -48683,9 +48242,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -48834,9 +48390,6 @@
       <c r="P253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -49086,7 +48639,7 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN254" t="b">
@@ -49236,9 +48789,6 @@
       <c r="P255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -49488,7 +49038,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -49638,9 +49188,6 @@
       <c r="P257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -49890,7 +49437,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -50040,9 +49587,6 @@
       <c r="P259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -50292,7 +49836,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -50439,9 +49983,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -50590,9 +50131,6 @@
       <c r="P262" t="n">
         <v>0</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0</v>
       </c>
@@ -50842,7 +50380,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -50992,9 +50530,6 @@
       <c r="P264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -51244,7 +50779,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -51394,9 +50929,6 @@
       <c r="P266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -51646,7 +51178,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -51796,9 +51328,6 @@
       <c r="P268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -52048,7 +51577,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -52195,9 +51724,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -52346,9 +51872,6 @@
       <c r="P271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -52598,7 +52121,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -52748,9 +52271,6 @@
       <c r="P273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -53000,7 +52520,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -53150,9 +52670,6 @@
       <c r="P275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -53402,7 +52919,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -53552,9 +53069,6 @@
       <c r="P277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -53804,7 +53318,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -53954,9 +53468,6 @@
       <c r="P279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -54206,7 +53717,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -54353,9 +53864,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -54504,9 +54012,6 @@
       <c r="P282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -54756,7 +54261,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -54906,9 +54411,6 @@
       <c r="P284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -55158,7 +54660,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -55308,9 +54810,6 @@
       <c r="P286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -55560,7 +55059,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -55710,9 +55209,6 @@
       <c r="P288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -55962,7 +55458,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">

--- a/diseases/d203/2010-2014.xlsx
+++ b/diseases/d203/2010-2014.xlsx
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17835,7 +17835,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -24001,7 +24001,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24799,7 +24799,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -25198,7 +25198,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26540,7 +26540,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -27338,7 +27338,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -27882,7 +27882,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -28281,7 +28281,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -29079,7 +29079,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -30022,7 +30022,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -30421,7 +30421,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -31763,7 +31763,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -32960,7 +32960,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -33504,7 +33504,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -33903,7 +33903,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -34701,7 +34701,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
@@ -35245,7 +35245,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -35644,7 +35644,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -36043,7 +36043,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -36442,7 +36442,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -37385,7 +37385,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -37784,7 +37784,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39126,7 +39126,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -39525,7 +39525,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -40323,7 +40323,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -40867,7 +40867,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -41266,7 +41266,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -41665,7 +41665,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -43007,7 +43007,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -44204,7 +44204,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -44748,7 +44748,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -45147,7 +45147,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK236" t="inlineStr">
@@ -45546,7 +45546,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -45945,7 +45945,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -46489,7 +46489,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -46888,7 +46888,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -47287,7 +47287,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -47686,7 +47686,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -48085,7 +48085,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -48629,7 +48629,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -49028,7 +49028,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -49427,7 +49427,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -49826,7 +49826,7 @@
       </c>
       <c r="AJ260" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK260" t="inlineStr">
@@ -50370,7 +50370,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -50769,7 +50769,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -51168,7 +51168,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51567,7 +51567,7 @@
       </c>
       <c r="AJ269" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK269" t="inlineStr">
@@ -52111,7 +52111,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52510,7 +52510,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -52909,7 +52909,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -53308,7 +53308,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
@@ -53707,7 +53707,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -54251,7 +54251,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -54650,7 +54650,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -55049,7 +55049,7 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
@@ -55448,7 +55448,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
